--- a/ARM Functions/CRO size changer attempt.xlsx
+++ b/ARM Functions/CRO size changer attempt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF5AF95-DB50-4403-B18F-531919F66834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF442D1F-6F9D-4D53-8F27-7B83056112D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" activeTab="3" xr2:uid="{36E89F47-A927-490A-B5B6-7F384079C93D}"/>
+    <workbookView xWindow="-19200" yWindow="7260" windowWidth="24686" windowHeight="11220" activeTab="3" xr2:uid="{36E89F47-A927-490A-B5B6-7F384079C93D}"/>
   </bookViews>
   <sheets>
     <sheet name="CRO Header" sheetId="2" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="318">
   <si>
     <t>address</t>
   </si>
@@ -1021,9 +1021,6 @@
   </si>
   <si>
     <t>42 43 04 00 02 00 00 00 38 B3 0D 00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp; </t>
   </si>
 </sst>
 </file>
@@ -21360,8 +21357,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H24" t="s">
-        <v>318</v>
+      <c r="H24" t="str">
+        <f t="shared" si="6"/>
+        <v>00000000</v>
       </c>
     </row>
     <row r="25" spans="1:13">
